--- a/survey_templates/050_remote_employee_connectivity_and_morale_check_in--survey_templates.xlsx
+++ b/survey_templates/050_remote_employee_connectivity_and_morale_check_in--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'customer_support'}</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Customer Support'}</t>
+          <t>Customer Support</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'alex'}</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Alex'}</t>
+          <t>Alex</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'mike'}</t>
+          <t>mike</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Mike'}</t>
+          <t>Mike</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'sam'}</t>
+          <t>sam</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Sam'}</t>
+          <t>Sam</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'alex'}</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Alex'}</t>
+          <t>Alex</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'mike'}</t>
+          <t>mike</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Mike'}</t>
+          <t>Mike</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'sam'}</t>
+          <t>sam</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Sam'}</t>
+          <t>Sam</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'alex'}</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Alex'}</t>
+          <t>Alex</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'mike'}</t>
+          <t>mike</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Mike'}</t>
+          <t>Mike</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'mike'}</t>
+          <t>mike</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Mike'}</t>
+          <t>Mike</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'cst'}</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'CST'}</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'mst'}</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'MST'}</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'PST'}</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
